--- a/Herman_sim/bachelor_montecarlo/model_mc_ready_2.xlsx
+++ b/Herman_sim/bachelor_montecarlo/model_mc_ready_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studntnu-my.sharepoint.com/personal/hermaose_ntnu_no/Documents/Programmering Bachelor/Transport-under-usikkerhet---Monte-Carlo/Herman_sim/bachelor_montecarlo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A60CC42F-6E5A-41A1-89E9-4646EF54B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3FA1892-C43B-4AF6-A8E8-2E4DA719B131}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{A60CC42F-6E5A-41A1-89E9-4646EF54B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5756F43-2740-412B-9E23-F3321984F9FB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ruter" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="170">
   <si>
     <t>faktorer</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Bratislava</t>
   </si>
   <si>
-    <t xml:space="preserve">Sjø fast kostnad RoRo </t>
-  </si>
-  <si>
     <t>Terminal transfer</t>
   </si>
   <si>
@@ -544,6 +541,12 @@
   </si>
   <si>
     <t xml:space="preserve">  Brukes til å verdsette redusert ledetidsvariabilitet (Andersson et al. 2017).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sjø kostnad pr kilometer - RoRo </t>
+  </si>
+  <si>
+    <t>UNCTAD (2023); RoRo-bransje 5-10 kr/km, midtpunkt valgt"</t>
   </si>
 </sst>
 </file>
@@ -554,7 +557,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_-&quot;kr &quot;* #,##0.00_-;&quot;-kr &quot;* #,##0.00_-;_-&quot;kr &quot;* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -625,8 +628,14 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -692,8 +701,44 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor rgb="FFB4B4B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -721,75 +766,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top/>
@@ -867,7 +843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -875,32 +851,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -909,24 +871,35 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,6 +973,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFFFF99"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1314,16 +1290,16 @@
                 <c:formatCode>_-"kr "* #\ ##0.00_-;"-kr "* #\ ##0.00_-;_-"kr "* \-??_-;_-@_-</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>121864.14285714286</c:v>
+                  <c:v>121976.14285714286</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>110654.14285714286</c:v>
+                  <c:v>110766.14285714286</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>108549</c:v>
+                  <c:v>107261</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>118629</c:v>
+                  <c:v>117341</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2678,7 +2654,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -2686,348 +2662,348 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10">
+        <v>64</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="6">
         <v>900</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="6">
         <v>28</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="7">
         <f>H2/I2</f>
         <v>32.142857142857146</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="6">
         <v>12</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="6">
         <v>34</v>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="7">
         <f>J2+K2+L2+O2</f>
         <v>78.642857142857139</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="6">
         <v>1</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="33">
         <v>0.5</v>
       </c>
-      <c r="P2" s="3"/>
+      <c r="P2" s="6"/>
     </row>
     <row r="3" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="10">
+        <v>64</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="6">
         <v>1200</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="6">
         <v>25</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="7">
         <f>H3/I3</f>
         <v>48</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="6">
         <v>6</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="6">
         <f>IF(E3="Sjø",18,IF(E3="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="7">
         <f>J3+K3+L3+O3</f>
         <v>78</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="6">
         <v>0</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="33">
         <v>0</v>
       </c>
-      <c r="P3" s="3"/>
+      <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10">
+        <v>64</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="F4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="10">
+      <c r="H4" s="6">
         <v>20</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="6">
         <v>60</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="7">
         <f>H4/I4</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="6">
         <v>4</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="6">
         <f>IF(E4="Sjø",18,IF(E4="Truck",0,24))</f>
         <v>0</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="7">
         <f>J4+K4+L4+O4</f>
         <v>4.333333333333333</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="6">
         <v>1</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="33">
         <v>0</v>
       </c>
-      <c r="P4" s="3"/>
+      <c r="P4" s="6"/>
     </row>
     <row r="5" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10">
+        <v>64</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="E5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="10">
+      <c r="G5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="6">
         <v>400</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="6">
         <v>25</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="7">
         <f>H5/I5</f>
         <v>16</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="6">
         <v>6</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="6">
         <f>IF(E5="Sjø",18,IF(E5="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="7">
         <f>J5+K5+L5+O5</f>
         <v>46</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="6">
         <v>0</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="33">
         <v>0</v>
       </c>
-      <c r="P5" s="3"/>
+      <c r="P5" s="6"/>
     </row>
     <row r="6" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10">
+        <v>64</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="F6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="10">
+      <c r="H6" s="6">
         <v>500</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="6">
         <v>25</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="7">
         <f>H6/I6</f>
         <v>20</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="6">
         <v>4</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="6">
         <f>IF(E6="Sjø",18,IF(E6="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="7">
         <f>J6+K6+L6+O6</f>
         <v>51</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="6">
         <v>1</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="33">
         <v>3</v>
       </c>
-      <c r="P6" s="3"/>
+      <c r="P6" s="6"/>
     </row>
     <row r="7" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="14">
+      <c r="B7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="8">
         <f>COUNT(C2:C6)</f>
         <v>5</v>
       </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8">
         <f>SUM(H2:H6)</f>
         <v>3020</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="15">
+      <c r="I7" s="8"/>
+      <c r="J7" s="9">
         <f t="shared" ref="J7:O7" si="0">SUM(J2:J6)</f>
         <v>116.47619047619047</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="8">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="34">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="M7" s="17">
+      <c r="M7" s="9">
         <f t="shared" si="0"/>
         <v>257.97619047619048</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="8">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="34">
         <f t="shared" si="0"/>
         <v>3.5</v>
       </c>
-      <c r="P7" s="18">
+      <c r="P7" s="40">
         <f>M7/24</f>
         <v>10.749007936507937</v>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="10">
         <v>7.5</v>
       </c>
       <c r="R7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -3045,289 +3021,293 @@
         <v>7</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="L10" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="20" t="s">
+      <c r="M10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="O10" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="O10" s="9" t="s">
+      <c r="P10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="Q10" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="Q10" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10">
+        <v>67</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6">
         <v>1</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="10">
+      <c r="G11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="6">
         <v>900</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="6">
         <v>28</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="7">
         <f>H11/I11</f>
         <v>32.142857142857146</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="6">
         <v>12</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="6">
         <f>IF(E11="Sjø",34,IF(E11="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="7">
         <f>J11+K11+L11+O11</f>
         <v>78.642857142857139</v>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="6">
         <v>1</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="33">
         <v>0.5</v>
       </c>
+      <c r="P11" s="33"/>
     </row>
     <row r="12" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>68</v>
-      </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10">
+        <v>67</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6">
         <v>2</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="10">
+      <c r="H12" s="6">
         <v>840</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="6">
         <v>25</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="7">
         <f>H12/I12</f>
         <v>33.6</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="6">
         <v>6</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="6">
         <f>IF(E12="Sjø",18,IF(E12="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="7">
         <f>J12+K12+L12+O12</f>
         <v>63.6</v>
       </c>
-      <c r="N12" s="10">
+      <c r="N12" s="6">
         <v>0</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="33">
         <v>0</v>
       </c>
+      <c r="P12" s="33"/>
     </row>
     <row r="13" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10">
+        <v>67</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
         <v>3</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="G13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H13" s="10">
+      <c r="H13" s="6">
         <v>400</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="6">
         <v>25</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="7">
         <f>H13/I13</f>
         <v>16</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="6">
         <v>6</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="6">
         <f>IF(E13="Sjø",18,IF(E13="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M13" s="11">
+      <c r="M13" s="7">
         <f>J13+K13+L13+O13</f>
         <v>46</v>
       </c>
-      <c r="N13" s="10">
+      <c r="N13" s="6">
         <v>0</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="33">
         <v>0</v>
       </c>
+      <c r="P13" s="33"/>
     </row>
     <row r="14" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="10">
+        <v>67</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6">
         <v>4</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="10">
+      <c r="D14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="6">
         <v>550</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="6">
         <v>25</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="7">
         <f>H14/I14</f>
         <v>22</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="6">
         <v>4</v>
       </c>
-      <c r="L14" s="21">
+      <c r="L14" s="6">
         <f>IF(E14="Sjø",18,IF(E14="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M14" s="11">
+      <c r="M14" s="7">
         <f>J14+K14+L14+O14</f>
         <v>53</v>
       </c>
-      <c r="N14" s="10">
+      <c r="N14" s="6">
         <v>1</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="33">
         <v>3</v>
       </c>
+      <c r="P14" s="33"/>
     </row>
     <row r="15" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="22">
+      <c r="B15" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="38">
         <f>COUNT(C11:C14)</f>
         <v>4</v>
       </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22">
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38">
         <f>SUM(H11:H14)</f>
         <v>2690</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="23">
+      <c r="I15" s="38"/>
+      <c r="J15" s="39">
         <f t="shared" ref="J15:O15" si="1">SUM(J11:J14)</f>
         <v>103.74285714285715</v>
       </c>
-      <c r="K15" s="22">
+      <c r="K15" s="38">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="L15" s="21">
+      <c r="L15" s="38">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="39">
         <f t="shared" si="1"/>
         <v>241.24285714285713</v>
       </c>
-      <c r="N15" s="22">
+      <c r="N15" s="38">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="32">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="10">
         <f>M15/24</f>
         <v>10.051785714285714</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J16" s="24"/>
-      <c r="M16" s="24"/>
+      <c r="J16" s="11"/>
+      <c r="M16" s="11"/>
     </row>
     <row r="17" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J17" s="24"/>
-      <c r="M17" s="24"/>
+      <c r="J17" s="11"/>
+      <c r="M17" s="11"/>
     </row>
     <row r="18" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J18" s="24"/>
-      <c r="M18" s="24"/>
+      <c r="J18" s="11"/>
+      <c r="M18" s="11"/>
     </row>
     <row r="21" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -3345,255 +3325,263 @@
         <v>7</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="L21" s="20" t="s">
+      <c r="M21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="O21" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="O21" s="9" t="s">
+      <c r="P21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="P21" s="8" t="s">
+      <c r="Q21" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="Q21" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>69</v>
-      </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10">
+        <v>68</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6">
         <v>1</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10" t="s">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H22" s="10">
+      <c r="G22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="6">
         <v>700</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="6">
         <v>28</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="6">
         <f>H22/I22</f>
         <v>25</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="6">
         <v>12</v>
       </c>
-      <c r="L22" s="25">
+      <c r="L22" s="37">
         <f>IF(E22="Sjø",34,IF(E22="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="6">
         <f>J22+K22+L22+O22</f>
         <v>71.5</v>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="6">
         <v>1</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="33">
         <v>0.5</v>
       </c>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
     </row>
     <row r="23" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>69</v>
-      </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10">
+        <v>68</v>
+      </c>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6">
         <v>2</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="10" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="H23" s="10">
+      <c r="H23" s="6">
         <v>850</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="6">
         <v>25</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="6">
         <f>H23/I23</f>
         <v>34</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="6">
         <v>6</v>
       </c>
-      <c r="L23" s="25">
+      <c r="L23" s="37">
         <f>IF(E23="Sjø",18,IF(E23="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M23" s="10">
+      <c r="M23" s="6">
         <f>J23+K23+L23+O23</f>
         <v>64</v>
       </c>
-      <c r="N23" s="10">
+      <c r="N23" s="6">
         <v>0</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="33">
         <v>0</v>
       </c>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
     </row>
     <row r="24" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10">
+        <v>68</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6">
         <v>3</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H24" s="10">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H24" s="6">
         <v>400</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="6">
         <v>25</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="6">
         <f>H24/I24</f>
         <v>16</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="6">
         <v>6</v>
       </c>
-      <c r="L24" s="25">
+      <c r="L24" s="37">
         <f>IF(E24="Sjø",18,IF(E24="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="6">
         <f>J24+K24+L24+O24</f>
         <v>46</v>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="6">
         <v>0</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="33">
         <v>0</v>
       </c>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
     </row>
     <row r="25" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10">
+        <v>68</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6">
         <v>4</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H25" s="10">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="6">
         <v>550</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="6">
         <v>25</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="6">
         <f>H25/I25</f>
         <v>22</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="6">
         <v>4</v>
       </c>
-      <c r="L25" s="25">
+      <c r="L25" s="37">
         <f>IF(E25="Sjø",18,IF(E25="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M25" s="10">
+      <c r="M25" s="6">
         <f>J25+K25+L25+O25</f>
         <v>53</v>
       </c>
-      <c r="N25" s="10">
+      <c r="N25" s="6">
         <v>1</v>
       </c>
-      <c r="O25">
+      <c r="O25" s="33">
         <v>3</v>
       </c>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
     </row>
     <row r="26" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14">
+      <c r="B26" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8">
         <f>SUM(H22:H25)</f>
         <v>2500</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14">
+      <c r="I26" s="8"/>
+      <c r="J26" s="8">
         <f t="shared" ref="J26:O26" si="2">SUM(J22:J25)</f>
         <v>97</v>
       </c>
-      <c r="K26" s="14">
+      <c r="K26" s="8">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="L26" s="26">
+      <c r="L26" s="8">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="M26" s="14">
+      <c r="M26" s="8">
         <f t="shared" si="2"/>
         <v>234.5</v>
       </c>
-      <c r="N26" s="14">
+      <c r="N26" s="8">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="34">
         <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
@@ -3605,12 +3593,12 @@
         <v>9</v>
       </c>
       <c r="R26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="10" t="s">
-        <v>48</v>
+      <c r="B31" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -3628,263 +3616,263 @@
         <v>7</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K31" s="2" t="s">
+      <c r="L31" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="L31" s="20" t="s">
+      <c r="M31" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="O31" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="O31" s="9" t="s">
+      <c r="P31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="P31" s="8" t="s">
+      <c r="Q31" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="Q31" s="8" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10">
+        <v>69</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6">
         <v>1</v>
       </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10" t="s">
+      <c r="D32" s="6"/>
+      <c r="E32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="H32" s="10">
+      <c r="G32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="6">
         <v>700</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="6">
         <v>28</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="6">
         <f>H32/I32</f>
         <v>25</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="6">
         <v>12</v>
       </c>
-      <c r="L32" s="25">
+      <c r="L32" s="37">
         <f>IF(E32="Sjø",34,IF(E32="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M32" s="10">
+      <c r="M32" s="6">
         <f>J32+K32+L32+O32</f>
         <v>71.5</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N32" s="6">
         <v>1</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="33">
         <v>0.5</v>
       </c>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
     </row>
     <row r="33" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10">
+        <v>69</v>
+      </c>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6">
         <v>2</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H33" s="10">
+      <c r="D33" s="6"/>
+      <c r="E33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="6">
         <v>1100</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="6">
         <v>25</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="6">
         <f>H33/I33</f>
         <v>44</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="6">
         <v>6</v>
       </c>
-      <c r="L33" s="25">
+      <c r="L33" s="37">
         <f>IF(E33="Sjø",18,IF(E33="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M33" s="10">
+      <c r="M33" s="6">
         <f>J33+K33+L33+O33</f>
         <v>74</v>
       </c>
-      <c r="N33" s="10">
+      <c r="N33" s="6">
         <v>0</v>
       </c>
-      <c r="O33">
+      <c r="O33" s="33">
         <v>0</v>
       </c>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
     </row>
     <row r="34" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10">
+        <v>69</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6">
         <v>3</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F34" s="10" t="s">
+      <c r="D34" s="6"/>
+      <c r="E34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H34" s="10">
+      <c r="H34" s="6">
         <v>500</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="6">
         <v>25</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="6">
         <f>H34/I34</f>
         <v>20</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="6">
         <v>6</v>
       </c>
-      <c r="L34" s="25">
+      <c r="L34" s="37">
         <f>IF(E34="Sjø",18,IF(E34="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M34" s="10">
+      <c r="M34" s="6">
         <f>J34+K34+L34+O34</f>
         <v>50</v>
       </c>
-      <c r="N34" s="10">
+      <c r="N34" s="6">
         <v>0</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="33">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
     </row>
     <row r="35" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10">
+        <v>69</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6">
         <v>4</v>
       </c>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G35" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="10">
+      <c r="D35" s="6"/>
+      <c r="E35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="6">
         <v>600</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="6">
         <v>25</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="6">
         <f>H35/I35</f>
         <v>24</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="6">
         <v>4</v>
       </c>
-      <c r="L35" s="25">
+      <c r="L35" s="37">
         <f>IF(E35="Sjø",18,IF(E35="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M35" s="10">
+      <c r="M35" s="6">
         <f>J35+K35+L35+O35</f>
         <v>55</v>
       </c>
-      <c r="N35" s="10">
+      <c r="N35" s="6">
         <v>1</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="33">
         <v>3</v>
       </c>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
     </row>
     <row r="36" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14">
+      <c r="B36" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8">
         <f>SUM(H32:H35)</f>
         <v>2900</v>
       </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14">
+      <c r="I36" s="8"/>
+      <c r="J36" s="8">
         <f t="shared" ref="J36:O36" si="3">SUM(J32:J35)</f>
         <v>113</v>
       </c>
-      <c r="K36" s="14">
+      <c r="K36" s="8">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="L36" s="26">
+      <c r="L36" s="8">
         <f t="shared" si="3"/>
         <v>106</v>
       </c>
-      <c r="M36" s="14">
+      <c r="M36" s="8">
         <f t="shared" si="3"/>
         <v>250.5</v>
       </c>
-      <c r="N36" s="14">
+      <c r="N36" s="8">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="34">
         <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
@@ -3896,242 +3884,254 @@
         <v>7</v>
       </c>
       <c r="R36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="B39" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="G39" t="s">
+      <c r="G39" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="H39" t="s">
-        <v>55</v>
-      </c>
-      <c r="I39" t="s">
-        <v>67</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="H39" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="J39" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="K39" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="L39" t="s">
+      <c r="M39" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="M39" t="s">
+      <c r="N39" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="N39" t="s">
+      <c r="O39" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="P39" t="s">
+      <c r="Q39" t="s">
         <v>63</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C40">
+        <v>71</v>
+      </c>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33">
         <v>1</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G40" t="s">
-        <v>46</v>
-      </c>
-      <c r="H40">
+      <c r="G40" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H40" s="33">
         <v>700</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="33">
         <v>28</v>
       </c>
-      <c r="J40">
+      <c r="J40" s="33">
         <f>H40/I40</f>
         <v>25</v>
       </c>
-      <c r="K40">
+      <c r="K40" s="33">
         <v>12</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="33">
         <f>IF(E40="Sjø",34,IF(E40="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M40">
+      <c r="M40" s="33">
         <f>J40+K40+L40+O40</f>
         <v>71.5</v>
       </c>
-      <c r="N40">
+      <c r="N40" s="33">
         <v>1</v>
       </c>
-      <c r="O40">
+      <c r="O40" s="33">
         <v>0.5</v>
       </c>
+      <c r="P40" s="33"/>
     </row>
     <row r="41" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41">
+        <v>71</v>
+      </c>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33">
         <v>2</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F41" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" t="s">
-        <v>53</v>
-      </c>
-      <c r="H41">
+      <c r="F41" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G41" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" s="33">
         <v>3800</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="33">
         <v>33</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="33">
         <f>H41/I41</f>
         <v>115.15151515151516</v>
       </c>
-      <c r="K41">
+      <c r="K41" s="33">
         <v>12</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="33">
         <f>IF(E41="Sjø",34,IF(E41="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M41">
+      <c r="M41" s="33">
         <f>J41+K41+L41+O41</f>
         <v>161.15151515151516</v>
       </c>
-      <c r="N41">
-        <v>1</v>
-      </c>
-      <c r="O41">
+      <c r="N41" s="33">
         <v>0</v>
       </c>
+      <c r="O41" s="33">
+        <v>0</v>
+      </c>
+      <c r="P41" s="33"/>
     </row>
     <row r="42" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42">
+        <v>71</v>
+      </c>
+      <c r="B42" s="33"/>
+      <c r="C42" s="33">
         <v>3</v>
       </c>
-      <c r="D42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E42" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" t="s">
-        <v>53</v>
-      </c>
-      <c r="G42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H42">
+      <c r="D42" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="H42" s="33">
         <v>476</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="33">
         <v>60</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="33">
         <f>H42/I42</f>
         <v>7.9333333333333336</v>
       </c>
-      <c r="K42">
+      <c r="K42" s="33">
         <v>4</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="33">
         <f>IF(E42="Sjø",18,IF(E42="Truck",0,24))</f>
         <v>0</v>
       </c>
-      <c r="M42">
+      <c r="M42" s="33">
         <f>J42+K42+L42+O42</f>
         <v>14.933333333333334</v>
       </c>
-      <c r="N42">
+      <c r="N42" s="33">
         <v>1</v>
       </c>
-      <c r="O42">
+      <c r="O42" s="33">
         <v>3</v>
       </c>
+      <c r="P42" s="33"/>
     </row>
     <row r="43" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B43" t="s">
-        <v>36</v>
-      </c>
-      <c r="C43">
+      <c r="B43" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="34">
         <f>COUNT(C40:C42)</f>
         <v>3</v>
       </c>
-      <c r="H43">
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34">
         <f>SUM(H40:H42)</f>
         <v>4976</v>
       </c>
-      <c r="J43">
+      <c r="I43" s="34"/>
+      <c r="J43" s="34">
         <f t="shared" ref="J43:O43" si="4">SUM(J40:J42)</f>
         <v>148.08484848484849</v>
       </c>
-      <c r="K43">
+      <c r="K43" s="34">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="34">
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="M43">
+      <c r="M43" s="34">
         <f t="shared" si="4"/>
         <v>247.58484848484849</v>
       </c>
-      <c r="N43">
+      <c r="N43" s="34">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="O43">
+        <v>2</v>
+      </c>
+      <c r="O43" s="34">
         <f t="shared" si="4"/>
         <v>3.5</v>
       </c>
-      <c r="P43">
+      <c r="P43" s="42">
         <f>M43/24</f>
         <v>10.316035353535353</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -4194,20 +4194,20 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="13">
         <v>330</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10">
+      <c r="G2" s="6"/>
+      <c r="H2" s="6">
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="6" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -4217,8 +4217,8 @@
         <v>17</v>
       </c>
       <c r="M2" s="3">
-        <f>B4</f>
-        <v>6188</v>
+        <f>B4*Ruter!H2</f>
+        <v>6300</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
@@ -4228,20 +4228,20 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="13">
         <v>0.5</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10">
+      <c r="G3" s="6"/>
+      <c r="H3" s="6">
         <v>2</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="6" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="3" t="s">
@@ -4260,26 +4260,29 @@
     </row>
     <row r="4" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6">
+        <v>3</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B4">
-        <v>6188</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10">
-        <v>3</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="K4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="M4" s="3">
         <f>$B$5*Ruter!H4*$B$9</f>
@@ -4291,30 +4294,30 @@
     </row>
     <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="27">
+        <v>26</v>
+      </c>
+      <c r="B5" s="13">
         <f>14/$B$9</f>
         <v>0.58333333333333337</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10">
+        <v>27</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6">
         <v>4</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>29</v>
+      <c r="J5" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M5" s="3">
         <f>$B$3*Ruter!H5*$B$9</f>
@@ -4326,26 +4329,26 @@
     </row>
     <row r="6" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>1688</v>
       </c>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10">
+      <c r="G6" s="6"/>
+      <c r="H6" s="6">
         <v>5</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="K6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="M6" s="3">
         <f>$B$3*Ruter!H6*$B$9</f>
@@ -4356,59 +4359,59 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="14">
+        <v>1200</v>
+      </c>
+      <c r="G7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="28">
-        <v>1200</v>
-      </c>
-      <c r="G7" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19">
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10">
         <f>SUM(M2:M6)</f>
-        <v>31668</v>
-      </c>
-      <c r="N7" s="19">
+        <v>31780</v>
+      </c>
+      <c r="N7" s="10">
         <f>$B$8*Ruter!N7</f>
         <v>5064</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="10">
         <f>B2*Ruter!M7</f>
         <v>85132.142857142855</v>
       </c>
-      <c r="P7" s="29">
+      <c r="P7" s="15">
         <f>SUM(M7:O7)</f>
-        <v>121864.14285714286</v>
+        <v>121976.14285714286</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="14">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="28">
-        <v>1688</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="27" t="s">
+      <c r="B9" s="13">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
         <v>38</v>
-      </c>
-      <c r="B9" s="27">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>3</v>
@@ -4439,46 +4442,46 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G11" s="10"/>
-      <c r="H11" s="10">
+      <c r="G11" s="6"/>
+      <c r="H11" s="6">
         <v>1</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="10" t="s">
-        <v>41</v>
+      <c r="L11" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="M11" s="3">
-        <f>B4</f>
-        <v>6188</v>
+        <f>B4*Ruter!H11</f>
+        <v>6300</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G12" s="10"/>
-      <c r="H12" s="10">
+      <c r="G12" s="6"/>
+      <c r="H12" s="6">
         <v>2</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>43</v>
       </c>
       <c r="M12" s="3">
         <f>$B$3*Ruter!H12*$B$9</f>
@@ -4489,21 +4492,21 @@
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G13" s="10"/>
-      <c r="H13" s="10">
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
         <v>3</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="L13" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>44</v>
       </c>
       <c r="M13" s="3">
         <f>$B$3*Ruter!H13*$B$9</f>
@@ -4514,21 +4517,21 @@
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G14" s="10"/>
-      <c r="H14" s="10">
+      <c r="G14" s="6"/>
+      <c r="H14" s="6">
         <v>4</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L14" s="10" t="s">
-        <v>34</v>
+      <c r="I14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="M14" s="3">
         <f>$B$3*Ruter!H14*$B$9</f>
@@ -4539,41 +4542,41 @@
       <c r="P14" s="3"/>
     </row>
     <row r="15" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G15" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="19">
+      <c r="G15" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="10">
         <f>SUM(M11:M14)</f>
-        <v>27668</v>
-      </c>
-      <c r="N15" s="19">
+        <v>27780</v>
+      </c>
+      <c r="N15" s="10">
         <f>$B$8*Ruter!N15</f>
         <v>3376</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="10">
         <f>$B$2*Ruter!M15</f>
         <v>79610.142857142855</v>
       </c>
-      <c r="P15" s="31">
+      <c r="P15" s="17">
         <f>SUM(M15:O15)</f>
-        <v>110654.14285714286</v>
+        <v>110766.14285714286</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P16" s="32"/>
+      <c r="P16" s="18"/>
     </row>
     <row r="17" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="18" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P18" s="32"/>
+      <c r="P18" s="18"/>
     </row>
     <row r="21" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>3</v>
@@ -4604,42 +4607,42 @@
       </c>
     </row>
     <row r="22" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G22" s="10"/>
-      <c r="H22" s="10">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6">
         <v>1</v>
       </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10" t="s">
+      <c r="I22" s="6"/>
+      <c r="J22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="K22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="10" t="s">
-        <v>46</v>
+      <c r="L22" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="M22" s="3">
-        <f>B4</f>
-        <v>6188</v>
+        <f>B4*Ruter!H22</f>
+        <v>4900</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
     </row>
     <row r="23" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G23" s="10"/>
-      <c r="H23" s="10">
+      <c r="G23" s="6"/>
+      <c r="H23" s="6">
         <v>2</v>
       </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K23" s="10" t="s">
+      <c r="I23" s="6"/>
+      <c r="J23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="L23" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="M23" s="3">
         <f>$B$3*Ruter!H23*$B$9</f>
@@ -4650,19 +4653,19 @@
       <c r="P23" s="3"/>
     </row>
     <row r="24" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G24" s="10"/>
-      <c r="H24" s="10">
+      <c r="G24" s="6"/>
+      <c r="H24" s="6">
         <v>3</v>
       </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="L24" s="10" t="s">
-        <v>44</v>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="M24" s="3">
         <f>$B$3*Ruter!H24*$B$9</f>
@@ -4673,19 +4676,19 @@
       <c r="P24" s="3"/>
     </row>
     <row r="25" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G25" s="10"/>
-      <c r="H25" s="10">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6">
         <v>4</v>
       </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="L25" s="10" t="s">
-        <v>34</v>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="M25" s="3">
         <f>$B$3*Ruter!H25*$B$9</f>
@@ -4696,37 +4699,37 @@
       <c r="P25" s="3"/>
     </row>
     <row r="26" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G26" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="19">
+      <c r="G26" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="10">
         <f>SUM(M22:M25)</f>
-        <v>27788</v>
-      </c>
-      <c r="N26" s="19">
+        <v>26500</v>
+      </c>
+      <c r="N26" s="10">
         <f>$B$8*Ruter!N26</f>
         <v>3376</v>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="10">
         <f>B2*Ruter!M26</f>
         <v>77385</v>
       </c>
-      <c r="P26" s="29">
+      <c r="P26" s="15">
         <f>SUM(M26:O26)</f>
-        <v>108549</v>
+        <v>107261</v>
       </c>
     </row>
     <row r="27" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P27" s="32"/>
+      <c r="P27" s="18"/>
     </row>
     <row r="30" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G30" s="10" t="s">
-        <v>48</v>
+      <c r="G30" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>3</v>
@@ -4757,42 +4760,42 @@
       </c>
     </row>
     <row r="31" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G31" s="10"/>
-      <c r="H31" s="10">
+      <c r="G31" s="6"/>
+      <c r="H31" s="6">
         <v>1</v>
       </c>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10" t="s">
+      <c r="I31" s="6"/>
+      <c r="J31" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="K31" s="10" t="s">
+      <c r="K31" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="L31" s="10" t="s">
-        <v>46</v>
+      <c r="L31" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="M31" s="3">
-        <f>B4</f>
-        <v>6188</v>
+        <f>B4*Ruter!H32</f>
+        <v>4900</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
     <row r="32" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G32" s="10"/>
-      <c r="H32" s="10">
+      <c r="G32" s="6"/>
+      <c r="H32" s="6">
         <v>2</v>
       </c>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="L32" s="10" t="s">
-        <v>49</v>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="M32" s="3">
         <f>$B$3*Ruter!H33*$B$9</f>
@@ -4803,19 +4806,19 @@
       <c r="P32" s="3"/>
     </row>
     <row r="33" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G33" s="10"/>
-      <c r="H33" s="10">
+      <c r="G33" s="6"/>
+      <c r="H33" s="6">
         <v>3</v>
       </c>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K33" s="10" t="s">
+      <c r="I33" s="6"/>
+      <c r="J33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="L33" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="M33" s="3">
         <f>$B$3*Ruter!H34*$B$9</f>
@@ -4826,19 +4829,19 @@
       <c r="P33" s="3"/>
     </row>
     <row r="34" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G34" s="10"/>
-      <c r="H34" s="10">
+      <c r="G34" s="6"/>
+      <c r="H34" s="6">
         <v>4</v>
       </c>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="L34" s="10" t="s">
-        <v>34</v>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="M34" s="3">
         <f>$B$3*Ruter!H35*$B$9</f>
@@ -4849,37 +4852,37 @@
       <c r="P34" s="3"/>
     </row>
     <row r="35" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G35" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="33"/>
-      <c r="M35" s="19">
+      <c r="G35" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="10">
         <f>SUM(M31:M34)</f>
-        <v>32588</v>
-      </c>
-      <c r="N35" s="19">
+        <v>31300</v>
+      </c>
+      <c r="N35" s="10">
         <f>$B$8*Ruter!N36</f>
         <v>3376</v>
       </c>
-      <c r="O35" s="19">
+      <c r="O35" s="10">
         <f>B2*Ruter!M36</f>
         <v>82665</v>
       </c>
-      <c r="P35" s="29">
+      <c r="P35" s="15">
         <f>SUM(M35:O35)</f>
-        <v>118629</v>
+        <v>117341</v>
       </c>
     </row>
     <row r="36" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P36" s="32"/>
+      <c r="P36" s="18"/>
     </row>
     <row r="39" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G39" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>3</v>
@@ -4924,11 +4927,11 @@
         <v>16</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M40" s="3">
-        <f>B4</f>
-        <v>6188</v>
+        <f>B4*Ruter!H40</f>
+        <v>4900</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -4946,14 +4949,14 @@
         <v>15</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M41" s="3">
-        <f>B4</f>
-        <v>6188</v>
+        <f>B4*Ruter!H41</f>
+        <v>26600</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
@@ -4965,16 +4968,16 @@
         <v>3</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M42" s="3">
         <f>$B$5*Ruter!H42*$B$9</f>
@@ -4985,29 +4988,29 @@
       <c r="P42" s="3"/>
     </row>
     <row r="43" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G43" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="19"/>
-      <c r="M43" s="19">
+      <c r="G43" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10">
         <f>SUM(M40:M42)</f>
-        <v>19040</v>
-      </c>
-      <c r="N43" s="19">
+        <v>38164</v>
+      </c>
+      <c r="N43" s="10">
         <f>$B$8*Ruter!N43</f>
-        <v>5064</v>
-      </c>
-      <c r="O43" s="19">
+        <v>3376</v>
+      </c>
+      <c r="O43" s="10">
         <f>$B$2*Ruter!M43</f>
         <v>81703</v>
       </c>
-      <c r="P43" s="31">
+      <c r="P43" s="17">
         <f>SUM(M43:O43)</f>
-        <v>105807</v>
+        <v>123243</v>
       </c>
     </row>
   </sheetData>
@@ -5028,59 +5031,59 @@
   <sheetData>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="34" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="32">
+      <c r="A3" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="18">
         <f>Kostnadsmodeller!P7</f>
-        <v>121864.14285714286</v>
-      </c>
-      <c r="C3" s="24">
+        <v>121976.14285714286</v>
+      </c>
+      <c r="C3" s="11">
         <f>Ruter!N7</f>
         <v>3</v>
       </c>
-      <c r="D3" s="35">
+      <c r="D3" s="21">
         <f>Ruter!M7</f>
         <v>257.97619047619048</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" s="32">
+      <c r="A4" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="18">
         <f>Kostnadsmodeller!P15</f>
-        <v>110654.14285714286</v>
-      </c>
-      <c r="C4" s="24">
+        <v>110766.14285714286</v>
+      </c>
+      <c r="C4" s="11">
         <f>Ruter!N15</f>
         <v>2</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="21">
         <f>Ruter!M15</f>
         <v>241.24285714285713</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="32">
+      <c r="A5" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="18">
         <f>Kostnadsmodeller!P26</f>
-        <v>108549</v>
+        <v>107261</v>
       </c>
       <c r="C5">
         <f>Ruter!N26</f>
@@ -5092,12 +5095,12 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="32">
+      <c r="A6" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="18">
         <f>Kostnadsmodeller!P35</f>
-        <v>118629</v>
+        <v>117341</v>
       </c>
       <c r="C6">
         <f>Ruter!N36</f>
@@ -5110,15 +5113,15 @@
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="32">
+        <v>71</v>
+      </c>
+      <c r="B7" s="18">
         <f>Kostnadsmodeller!P43</f>
-        <v>105807</v>
+        <v>123243</v>
       </c>
       <c r="C7">
         <f>Ruter!N43</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <f>Ruter!M43</f>
@@ -5146,556 +5149,556 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="39" t="s">
+      <c r="C5" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="D5" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="E5" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="39" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="26" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="40" t="s">
+      <c r="C6" s="27">
+        <v>0.12</v>
+      </c>
+      <c r="D6" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="41">
-        <v>0.12</v>
-      </c>
-      <c r="D6" s="40" t="s">
+      <c r="E6" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="40" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="26" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="40" t="s">
+      <c r="B7" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="27">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B7" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="41">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="40" t="s">
+      <c r="E7" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="E7" s="40" t="s">
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="40" t="s">
+      <c r="E8" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="40" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="D9" s="26" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="41">
-        <v>0.08</v>
-      </c>
-      <c r="D9" s="40" t="s">
+      <c r="E9" s="26" t="s">
         <v>90</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="25" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="39" t="s">
+      <c r="B13" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="C13" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="D13" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="E13" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="28">
+        <v>6</v>
+      </c>
+      <c r="C14" s="28">
+        <v>12</v>
+      </c>
+      <c r="D14" s="28">
+        <v>24</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="E13" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="42">
+      <c r="F14" s="26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="30">
+        <v>8</v>
+      </c>
+      <c r="C15" s="30">
+        <v>12</v>
+      </c>
+      <c r="D15" s="30">
+        <v>24</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="28">
+        <v>3</v>
+      </c>
+      <c r="C16" s="28">
         <v>6</v>
       </c>
-      <c r="C14" s="42">
+      <c r="D16" s="28">
         <v>12</v>
       </c>
-      <c r="D14" s="42">
-        <v>24</v>
-      </c>
-      <c r="E14" s="40" t="s">
-        <v>97</v>
-      </c>
-      <c r="F14" s="40" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="43" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" s="44">
+      <c r="E16" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="28">
+        <v>2</v>
+      </c>
+      <c r="C17" s="28">
+        <v>4</v>
+      </c>
+      <c r="D17" s="28">
         <v>8</v>
       </c>
-      <c r="C15" s="44">
-        <v>12</v>
-      </c>
-      <c r="D15" s="44">
-        <v>24</v>
-      </c>
-      <c r="E15" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="F15" s="43" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="42">
-        <v>3</v>
-      </c>
-      <c r="C16" s="42">
-        <v>6</v>
-      </c>
-      <c r="D16" s="42">
-        <v>12</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="40" t="s">
+      <c r="E17" s="26" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="42">
-        <v>2</v>
-      </c>
-      <c r="C17" s="42">
-        <v>4</v>
-      </c>
-      <c r="D17" s="42">
-        <v>8</v>
-      </c>
-      <c r="E17" s="40" t="s">
+      <c r="F17" s="26" t="s">
         <v>103</v>
-      </c>
-      <c r="F17" s="40" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="23" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="37" t="s">
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="25" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="39" t="s">
+      <c r="C22" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="D22" s="25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="28">
+        <v>68</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="D22" s="39" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="42">
+      <c r="D23" s="26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="28">
         <v>68</v>
       </c>
-      <c r="C23" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="40" t="s">
+      <c r="C24" s="26" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="42">
-        <v>68</v>
-      </c>
-      <c r="C24" s="40" t="s">
+      <c r="D24" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="D24" s="40" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="28">
+        <v>48</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="42">
-        <v>48</v>
-      </c>
-      <c r="C25" s="40" t="s">
+      <c r="D25" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="D25" s="40" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="30">
+        <v>0</v>
+      </c>
+      <c r="C26" s="29" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="44">
-        <v>0</v>
-      </c>
-      <c r="C26" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="43" t="s">
-        <v>104</v>
+      <c r="D26" s="29" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="47"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="24" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="25" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="39" t="s">
+      <c r="B30" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="B30" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="39" t="s">
+      <c r="B31" s="28">
+        <v>0.25</v>
+      </c>
+      <c r="C31" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="28">
+        <v>1</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="F31" s="26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="B32" s="28">
+        <v>2</v>
+      </c>
+      <c r="C32" s="28">
+        <v>3</v>
+      </c>
+      <c r="D32" s="28">
         <v>5</v>
       </c>
-      <c r="D30" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="B31" s="42">
-        <v>0.25</v>
-      </c>
-      <c r="C31" s="42">
-        <v>0.5</v>
-      </c>
-      <c r="D31" s="42">
-        <v>1</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="F31" s="40" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="40" t="s">
+      <c r="E32" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="42">
-        <v>2</v>
-      </c>
-      <c r="C32" s="42">
-        <v>3</v>
-      </c>
-      <c r="D32" s="42">
-        <v>5</v>
-      </c>
-      <c r="E32" s="40" t="s">
+      <c r="F32" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="F32" s="40" t="s">
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="26" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="40" t="s">
+      <c r="B33" s="28">
+        <v>0</v>
+      </c>
+      <c r="C33" s="28">
+        <v>0</v>
+      </c>
+      <c r="D33" s="28">
+        <v>0</v>
+      </c>
+      <c r="E33" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="B33" s="42">
-        <v>0</v>
-      </c>
-      <c r="C33" s="42">
-        <v>0</v>
-      </c>
-      <c r="D33" s="42">
-        <v>0</v>
-      </c>
-      <c r="E33" s="40" t="s">
+      <c r="F33" s="26" t="s">
         <v>125</v>
-      </c>
-      <c r="F33" s="40" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="36" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A36" s="38" t="s">
+      <c r="A36" s="24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" s="23" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A37" s="37" t="s">
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="46"/>
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="28">
+        <v>0.05</v>
+      </c>
+      <c r="C39" s="28">
+        <v>12</v>
+      </c>
+      <c r="D39" s="28">
+        <v>24</v>
+      </c>
+      <c r="E39" s="28">
+        <v>72</v>
+      </c>
+      <c r="F39" s="26" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="52"/>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="42">
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="28">
         <v>0.05</v>
       </c>
-      <c r="C39" s="42">
+      <c r="C40" s="28">
         <v>12</v>
       </c>
-      <c r="D39" s="42">
+      <c r="D40" s="28">
         <v>24</v>
       </c>
-      <c r="E39" s="42">
+      <c r="E40" s="28">
         <v>72</v>
       </c>
-      <c r="F39" s="40" t="s">
+      <c r="F40" s="26" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="42">
-        <v>0.05</v>
-      </c>
-      <c r="C40" s="42">
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="28">
+        <v>0.08</v>
+      </c>
+      <c r="C41" s="28">
         <v>12</v>
       </c>
-      <c r="D40" s="42">
+      <c r="D41" s="28">
         <v>24</v>
       </c>
-      <c r="E40" s="42">
+      <c r="E41" s="28">
         <v>72</v>
       </c>
-      <c r="F40" s="40" t="s">
+      <c r="F41" s="26" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="40" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="42">
-        <v>0.08</v>
-      </c>
-      <c r="C41" s="42">
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="28">
+        <v>0.03</v>
+      </c>
+      <c r="C42" s="28">
+        <v>4</v>
+      </c>
+      <c r="D42" s="28">
         <v>12</v>
       </c>
-      <c r="D41" s="42">
+      <c r="E42" s="28">
         <v>24</v>
       </c>
-      <c r="E41" s="42">
-        <v>72</v>
-      </c>
-      <c r="F41" s="40" t="s">
+      <c r="F42" s="26" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="B42" s="42">
-        <v>0.03</v>
-      </c>
-      <c r="C42" s="42">
-        <v>4</v>
-      </c>
-      <c r="D42" s="42">
-        <v>12</v>
-      </c>
-      <c r="E42" s="42">
-        <v>24</v>
-      </c>
-      <c r="F42" s="40" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+    </row>
+    <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="B45" s="47"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-    </row>
-    <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="50" t="s">
+      <c r="B46" s="45"/>
+      <c r="C46" s="45"/>
+      <c r="D46" s="45"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="46"/>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="B46" s="51"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="52"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="40" t="s">
+      <c r="B47" s="28">
+        <v>10000</v>
+      </c>
+      <c r="C47" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="42">
-        <v>10000</v>
-      </c>
-      <c r="C47" s="40" t="s">
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="26" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="40" t="s">
+      <c r="B48" s="28">
+        <v>42</v>
+      </c>
+      <c r="C48" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="42">
-        <v>42</v>
-      </c>
-      <c r="C48" s="40" t="s">
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="26" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="40" t="s">
+      <c r="B49" s="28">
+        <v>0</v>
+      </c>
+      <c r="C49" s="26" t="s">
         <v>139</v>
-      </c>
-      <c r="B49" s="42">
-        <v>0</v>
-      </c>
-      <c r="C49" s="40" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5704,12 +5707,12 @@
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="47"/>
-      <c r="B57" s="47"/>
-      <c r="C57" s="47"/>
-      <c r="D57" s="47"/>
-      <c r="E57" s="47"/>
-      <c r="F57" s="47"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="43"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5743,170 +5746,170 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="48" t="s">
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="B4" s="39" t="s">
+      <c r="C4" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="D4" s="25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="39" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="40" t="s">
+      <c r="B5" s="28">
+        <v>330</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="42">
-        <v>330</v>
-      </c>
-      <c r="C5" s="40" t="s">
+      <c r="D5" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="40" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="26" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="40" t="s">
+      <c r="B6" s="28">
+        <v>0.8</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="42">
-        <v>0.8</v>
-      </c>
-      <c r="C6" s="40" t="s">
+      <c r="D6" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="40" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="26" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="40" t="s">
+      <c r="B7" s="28">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="B7" s="42">
-        <v>0.5</v>
-      </c>
-      <c r="C7" s="40" t="s">
+      <c r="D7" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="40" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="26" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="40" t="s">
+      <c r="B8" s="28">
+        <v>0.58330000000000004</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="B8" s="42">
-        <v>0.58330000000000004</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="D8" s="40" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="26" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="40" t="s">
+      <c r="B9" s="31">
+        <v>7</v>
+      </c>
+      <c r="C9" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="45">
-        <v>7</v>
-      </c>
-      <c r="C9" s="40" t="s">
+      <c r="D9" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="D9" s="40" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="26" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="40" t="s">
+      <c r="B10" s="28">
+        <v>0</v>
+      </c>
+      <c r="C10" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="B10" s="42">
-        <v>0</v>
-      </c>
-      <c r="C10" s="40" t="s">
+      <c r="D10" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="40" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="26" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="40" t="s">
+      <c r="B11" s="28">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="B11" s="42">
-        <v>1000</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="40" t="s">
+      <c r="B12" s="28">
+        <v>24</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="42">
-        <v>24</v>
-      </c>
-      <c r="C12" s="40" t="s">
+      <c r="D12" s="26" t="s">
         <v>164</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="47" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="48" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="43"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="B16" s="47"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="48" t="s">
-        <v>168</v>
-      </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5919,4 +5922,10 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{09a10672-822f-4467-a5ba-5bb375967c05}" enabled="0" method="" siteId="{09a10672-822f-4467-a5ba-5bb375967c05}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/Herman_sim/bachelor_montecarlo/model_mc_ready_2.xlsx
+++ b/Herman_sim/bachelor_montecarlo/model_mc_ready_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studntnu-my.sharepoint.com/personal/hermaose_ntnu_no/Documents/Programmering Bachelor/Transport-under-usikkerhet---Monte-Carlo/Herman_sim/bachelor_montecarlo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{A60CC42F-6E5A-41A1-89E9-4646EF54B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5756F43-2740-412B-9E23-F3321984F9FB}"/>
+  <xr:revisionPtr revIDLastSave="99" documentId="13_ncr:1_{A60CC42F-6E5A-41A1-89E9-4646EF54B732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34FCD881-E8A3-4BB7-9D03-B25D4D5F8F6E}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="170">
   <si>
     <t>faktorer</t>
   </si>
@@ -228,15 +228,9 @@
     <t>Dager reist</t>
   </si>
   <si>
-    <t>Routsecanner</t>
-  </si>
-  <si>
     <t>R1</t>
   </si>
   <si>
-    <t>dager</t>
-  </si>
-  <si>
     <t>GJ Hastighet km/t</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
     <t>R4</t>
   </si>
   <si>
-    <t>dagaer</t>
-  </si>
-  <si>
     <t>R5</t>
   </si>
   <si>
@@ -547,6 +538,15 @@
   </si>
   <si>
     <t>UNCTAD (2023); RoRo-bransje 5-10 kr/km, midtpunkt valgt"</t>
+  </si>
+  <si>
+    <t>Rute R6</t>
+  </si>
+  <si>
+    <t>Lovpålagt hviletid (timer)</t>
+  </si>
+  <si>
+    <t>R6</t>
   </si>
 </sst>
 </file>
@@ -738,7 +738,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -839,11 +839,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -851,7 +864,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -888,9 +900,17 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2634,7 +2654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2652,7 +2672,7 @@
     <col min="14" max="14" width="11.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>53</v>
       </c>
@@ -2662,7 +2682,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -2686,322 +2706,334 @@
       <c r="K1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="39" t="s">
         <v>58</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O1" s="36" t="s">
+      <c r="P1" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="Q1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>900</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>28</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <f>H2/I2</f>
         <v>32.142857142857146</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>12</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>34</v>
       </c>
-      <c r="M2" s="7">
-        <f>J2+K2+L2+O2</f>
+      <c r="M2" s="6">
+        <f>J2+K2+L2+P2</f>
         <v>78.642857142857139</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="49">
+        <v>0</v>
+      </c>
+      <c r="O2" s="5">
         <v>1</v>
       </c>
-      <c r="O2" s="33">
+      <c r="P2" s="32">
         <v>0.5</v>
       </c>
-      <c r="P2" s="6"/>
-    </row>
-    <row r="3" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q2" s="44"/>
+    </row>
+    <row r="3" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6">
+        <v>63</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>1200</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>25</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <f>H3/I3</f>
         <v>48</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>6</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <f>IF(E3="Sjø",18,IF(E3="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M3" s="7">
-        <f>J3+K3+L3+O3</f>
+      <c r="M3" s="6">
+        <f>J3+K3+L3+P3</f>
         <v>78</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="48">
         <v>0</v>
       </c>
-      <c r="O3" s="33">
+      <c r="O3" s="5">
         <v>0</v>
       </c>
-      <c r="P3" s="6"/>
-    </row>
-    <row r="4" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P3" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="44"/>
+    </row>
+    <row r="4" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6">
+        <v>63</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>20</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>60</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <f>H4/I4</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>4</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <f>IF(E4="Sjø",18,IF(E4="Truck",0,24))</f>
         <v>0</v>
       </c>
-      <c r="M4" s="7">
-        <f>J4+K4+L4+O4</f>
+      <c r="M4" s="6">
+        <f>J4+K4+L4+P4</f>
         <v>4.333333333333333</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="48">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
         <v>1</v>
       </c>
-      <c r="O4" s="33">
+      <c r="P4" s="32">
         <v>0</v>
       </c>
-      <c r="P4" s="6"/>
-    </row>
-    <row r="5" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q4" s="44"/>
+    </row>
+    <row r="5" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6">
+        <v>63</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>400</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>25</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <f>H5/I5</f>
         <v>16</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>6</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <f>IF(E5="Sjø",18,IF(E5="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M5" s="7">
-        <f>J5+K5+L5+O5</f>
+      <c r="M5" s="6">
+        <f>J5+K5+L5+P5</f>
         <v>46</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="48">
         <v>0</v>
       </c>
-      <c r="O5" s="33">
+      <c r="O5" s="5">
         <v>0</v>
       </c>
-      <c r="P5" s="6"/>
-    </row>
-    <row r="6" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P5" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="44"/>
+    </row>
+    <row r="6" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6">
+        <v>63</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>500</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>25</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <f>H6/I6</f>
         <v>20</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>4</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <f>IF(E6="Sjø",18,IF(E6="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M6" s="7">
-        <f>J6+K6+L6+O6</f>
+      <c r="M6" s="6">
+        <f>J6+K6+L6+P6</f>
         <v>51</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="48">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
         <v>1</v>
       </c>
-      <c r="O6" s="33">
+      <c r="P6" s="32">
         <v>3</v>
       </c>
-      <c r="P6" s="6"/>
-    </row>
-    <row r="7" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="8" t="s">
+      <c r="Q6" s="44"/>
+    </row>
+    <row r="7" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <f>COUNT(C2:C6)</f>
         <v>5</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7">
         <f>SUM(H2:H6)</f>
         <v>3020</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9">
-        <f t="shared" ref="J7:O7" si="0">SUM(J2:J6)</f>
+      <c r="I7" s="7"/>
+      <c r="J7" s="8">
+        <f t="shared" ref="J7:M7" si="0">SUM(J2:J6)</f>
         <v>116.47619047619047</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="7">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="33">
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="M7" s="9">
+      <c r="M7" s="8">
         <f t="shared" si="0"/>
         <v>257.97619047619048</v>
       </c>
-      <c r="N7" s="8">
-        <f t="shared" si="0"/>
+      <c r="N7" s="31">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <f>SUM(O2:O6)</f>
         <v>3</v>
       </c>
-      <c r="O7" s="34">
-        <f t="shared" si="0"/>
+      <c r="P7" s="33">
+        <f>SUM(P2:P6)</f>
         <v>3.5</v>
       </c>
-      <c r="P7" s="40">
+      <c r="Q7" s="45">
         <f>M7/24</f>
         <v>10.749007936507937</v>
       </c>
-      <c r="Q7" s="10">
-        <v>7.5</v>
-      </c>
-      <c r="R7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="10" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B10" s="2" t="s">
         <v>39</v>
       </c>
@@ -3024,7 +3056,7 @@
         <v>54</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>56</v>
@@ -3032,280 +3064,295 @@
       <c r="K10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L10" s="35" t="s">
+      <c r="L10" s="34" t="s">
         <v>58</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="N10" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O10" s="36" t="s">
+      <c r="P10" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="Q10" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6">
+        <v>65</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
         <v>1</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>900</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>28</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <f>H11/I11</f>
         <v>32.142857142857146</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>12</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <f>IF(E11="Sjø",34,IF(E11="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M11" s="7">
-        <f>J11+K11+L11+O11</f>
+      <c r="M11" s="6">
+        <f>J11+K11+L11+P11</f>
         <v>78.642857142857139</v>
       </c>
-      <c r="N11" s="6">
+      <c r="N11" s="48">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5">
         <v>1</v>
       </c>
-      <c r="O11" s="33">
+      <c r="P11" s="32">
         <v>0.5</v>
       </c>
-      <c r="P11" s="33"/>
-    </row>
-    <row r="12" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q11" s="46"/>
+    </row>
+    <row r="12" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6">
+        <v>65</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>840</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>25</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <f>H12/I12</f>
         <v>33.6</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>6</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <f>IF(E12="Sjø",18,IF(E12="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M12" s="7">
-        <f>J12+K12+L12+O12</f>
+      <c r="M12" s="6">
+        <f>J12+K12+L12+P12</f>
         <v>63.6</v>
       </c>
-      <c r="N12" s="6">
+      <c r="N12" s="48">
         <v>0</v>
       </c>
-      <c r="O12" s="33">
+      <c r="O12" s="5">
         <v>0</v>
       </c>
-      <c r="P12" s="33"/>
-    </row>
-    <row r="13" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P12" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="46"/>
+    </row>
+    <row r="13" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6">
+        <v>65</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5">
         <v>3</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>400</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>25</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="6">
         <f>H13/I13</f>
         <v>16</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>6</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <f>IF(E13="Sjø",18,IF(E13="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M13" s="7">
-        <f>J13+K13+L13+O13</f>
+      <c r="M13" s="6">
+        <f>J13+K13+L13+P13</f>
         <v>46</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="48">
         <v>0</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="5">
         <v>0</v>
       </c>
-      <c r="P13" s="33"/>
-    </row>
-    <row r="14" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P13" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="46"/>
+    </row>
+    <row r="14" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6">
+        <v>65</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5">
         <v>4</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>550</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>25</v>
       </c>
-      <c r="J14" s="7">
+      <c r="J14" s="6">
         <f>H14/I14</f>
         <v>22</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>4</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <f>IF(E14="Sjø",18,IF(E14="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M14" s="7">
-        <f>J14+K14+L14+O14</f>
+      <c r="M14" s="6">
+        <f>J14+K14+L14+P14</f>
         <v>53</v>
       </c>
-      <c r="N14" s="6">
+      <c r="N14" s="48">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5">
         <v>1</v>
       </c>
-      <c r="O14" s="33">
+      <c r="P14" s="32">
         <v>3</v>
       </c>
-      <c r="P14" s="33"/>
-    </row>
-    <row r="15" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="38" t="s">
+      <c r="Q14" s="46"/>
+    </row>
+    <row r="15" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="37">
         <f>COUNT(C11:C14)</f>
         <v>4</v>
       </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38">
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37">
         <f>SUM(H11:H14)</f>
         <v>2690</v>
       </c>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39">
-        <f t="shared" ref="J15:O15" si="1">SUM(J11:J14)</f>
+      <c r="I15" s="37"/>
+      <c r="J15" s="38">
+        <f t="shared" ref="J15:M15" si="1">SUM(J11:J14)</f>
         <v>103.74285714285715</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15" s="37">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="L15" s="38">
+      <c r="L15" s="37">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
-      <c r="M15" s="39">
+      <c r="M15" s="38">
         <f t="shared" si="1"/>
         <v>241.24285714285713</v>
       </c>
-      <c r="N15" s="38">
-        <f t="shared" si="1"/>
+      <c r="N15" s="31">
+        <v>0</v>
+      </c>
+      <c r="O15" s="37">
+        <f>SUM(O11:O14)</f>
         <v>2</v>
       </c>
-      <c r="O15" s="32">
-        <f t="shared" si="1"/>
+      <c r="P15" s="31">
+        <f>SUM(P11:P14)</f>
         <v>3.5</v>
       </c>
-      <c r="P15" s="10">
+      <c r="Q15" s="9">
         <f>M15/24</f>
         <v>10.051785714285714</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J16" s="11"/>
-      <c r="M16" s="11"/>
-    </row>
-    <row r="17" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J17" s="11"/>
-      <c r="M17" s="11"/>
-    </row>
-    <row r="18" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="J18" s="11"/>
-      <c r="M18" s="11"/>
-    </row>
-    <row r="21" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J16" s="10"/>
+      <c r="M16" s="10"/>
+    </row>
+    <row r="17" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J17" s="10"/>
+      <c r="M17" s="10"/>
+    </row>
+    <row r="18" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="J18" s="10"/>
+      <c r="M18" s="10"/>
+    </row>
+    <row r="21" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="2" t="s">
         <v>44</v>
       </c>
@@ -3328,7 +3375,7 @@
         <v>54</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>56</v>
@@ -3336,268 +3383,273 @@
       <c r="K21" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="35" t="s">
+      <c r="L21" s="34" t="s">
         <v>58</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="N21" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O21" s="36" t="s">
+      <c r="P21" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="Q21" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="22" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6">
+        <v>66</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
         <v>1</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6" t="s">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>700</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>28</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="5">
         <f>H22/I22</f>
         <v>25</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>12</v>
       </c>
-      <c r="L22" s="37">
+      <c r="L22" s="36">
         <f>IF(E22="Sjø",34,IF(E22="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M22" s="6">
-        <f>J22+K22+L22+O22</f>
+      <c r="M22" s="5">
+        <f>J22+K22+L22+P22</f>
         <v>71.5</v>
       </c>
-      <c r="N22" s="6">
+      <c r="N22" s="48">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5">
         <v>1</v>
       </c>
-      <c r="O22" s="33">
+      <c r="P22" s="32">
         <v>0.5</v>
       </c>
-      <c r="P22" s="33"/>
-      <c r="Q22" s="33"/>
-    </row>
-    <row r="23" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q22" s="46"/>
+    </row>
+    <row r="23" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6">
+        <v>66</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5">
         <v>2</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6" t="s">
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>850</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>25</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="5">
         <f>H23/I23</f>
         <v>34</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>6</v>
       </c>
-      <c r="L23" s="37">
+      <c r="L23" s="36">
         <f>IF(E23="Sjø",18,IF(E23="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M23" s="6">
-        <f>J23+K23+L23+O23</f>
+      <c r="M23" s="5">
+        <f>J23+K23+L23+P23</f>
         <v>64</v>
       </c>
-      <c r="N23" s="6">
+      <c r="N23" s="48">
         <v>0</v>
       </c>
-      <c r="O23" s="33">
+      <c r="O23" s="5">
         <v>0</v>
       </c>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-    </row>
-    <row r="24" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P23" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="46"/>
+    </row>
+    <row r="24" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6">
+        <v>66</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5">
         <v>3</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="5"/>
+      <c r="E24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>400</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>25</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="5">
         <f>H24/I24</f>
         <v>16</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>6</v>
       </c>
-      <c r="L24" s="37">
+      <c r="L24" s="36">
         <f>IF(E24="Sjø",18,IF(E24="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M24" s="6">
-        <f>J24+K24+L24+O24</f>
+      <c r="M24" s="5">
+        <f>J24+K24+L24+P24</f>
         <v>46</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N24" s="48">
         <v>0</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="5">
         <v>0</v>
       </c>
-      <c r="P24" s="33"/>
-      <c r="Q24" s="33"/>
-    </row>
-    <row r="25" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P24" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="46"/>
+    </row>
+    <row r="25" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6">
+        <v>66</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5">
         <v>4</v>
       </c>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="5"/>
+      <c r="E25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>550</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>25</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="5">
         <f>H25/I25</f>
         <v>22</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>4</v>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="36">
         <f>IF(E25="Sjø",18,IF(E25="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M25" s="6">
-        <f>J25+K25+L25+O25</f>
+      <c r="M25" s="5">
+        <f>J25+K25+L25+P25</f>
         <v>53</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="48">
+        <v>0</v>
+      </c>
+      <c r="O25" s="5">
         <v>1</v>
       </c>
-      <c r="O25" s="33">
+      <c r="P25" s="32">
         <v>3</v>
       </c>
-      <c r="P25" s="33"/>
-      <c r="Q25" s="33"/>
-    </row>
-    <row r="26" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B26" s="8" t="s">
+      <c r="Q25" s="46"/>
+    </row>
+    <row r="26" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8">
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7">
         <f>SUM(H22:H25)</f>
         <v>2500</v>
       </c>
-      <c r="I26" s="8"/>
-      <c r="J26" s="8">
-        <f t="shared" ref="J26:O26" si="2">SUM(J22:J25)</f>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7">
+        <f t="shared" ref="J26:M26" si="2">SUM(J22:J25)</f>
         <v>97</v>
       </c>
-      <c r="K26" s="8">
+      <c r="K26" s="7">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="L26" s="8">
+      <c r="L26" s="7">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="M26" s="8">
+      <c r="M26" s="7">
         <f t="shared" si="2"/>
         <v>234.5</v>
       </c>
-      <c r="N26" s="8">
-        <f t="shared" si="2"/>
+      <c r="N26" s="31">
+        <v>0</v>
+      </c>
+      <c r="O26" s="7">
+        <f>SUM(O22:O25)</f>
         <v>2</v>
       </c>
-      <c r="O26" s="34">
-        <f t="shared" si="2"/>
+      <c r="P26" s="33">
+        <f>SUM(P22:P25)</f>
         <v>3.5</v>
       </c>
-      <c r="P26" s="19">
+      <c r="Q26" s="47">
         <f>M26/24</f>
         <v>9.7708333333333339</v>
       </c>
-      <c r="Q26" s="19">
-        <v>9</v>
-      </c>
-      <c r="R26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="6" t="s">
+    </row>
+    <row r="31" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -3619,7 +3671,7 @@
         <v>54</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>56</v>
@@ -3627,507 +3679,725 @@
       <c r="K31" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="L31" s="35" t="s">
+      <c r="L31" s="34" t="s">
         <v>58</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="N31" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="O31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O31" s="36" t="s">
+      <c r="P31" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="P31" s="2" t="s">
+      <c r="Q31" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="Q31" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="32" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>69</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6">
+        <v>67</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5">
         <v>1</v>
       </c>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6" t="s">
+      <c r="D32" s="5"/>
+      <c r="E32" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="5">
         <v>700</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="5">
         <v>28</v>
       </c>
-      <c r="J32" s="6">
+      <c r="J32" s="5">
         <f>H32/I32</f>
         <v>25</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>12</v>
       </c>
-      <c r="L32" s="37">
+      <c r="L32" s="36">
         <f>IF(E32="Sjø",34,IF(E32="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M32" s="6">
-        <f>J32+K32+L32+O32</f>
+      <c r="M32" s="5">
+        <f>J32+K32+L32+P32</f>
         <v>71.5</v>
       </c>
-      <c r="N32" s="6">
+      <c r="N32" s="48">
+        <v>0</v>
+      </c>
+      <c r="O32" s="5">
         <v>1</v>
       </c>
-      <c r="O32" s="33">
+      <c r="P32" s="32">
         <v>0.5</v>
       </c>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-    </row>
-    <row r="33" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q32" s="44"/>
+    </row>
+    <row r="33" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>69</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6">
+        <v>67</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5">
         <v>2</v>
       </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6" t="s">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="5">
         <v>1100</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="5">
         <v>25</v>
       </c>
-      <c r="J33" s="6">
+      <c r="J33" s="5">
         <f>H33/I33</f>
         <v>44</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>6</v>
       </c>
-      <c r="L33" s="37">
+      <c r="L33" s="36">
         <f>IF(E33="Sjø",18,IF(E33="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M33" s="6">
-        <f>J33+K33+L33+O33</f>
+      <c r="M33" s="5">
+        <f>J33+K33+L33+P33</f>
         <v>74</v>
       </c>
-      <c r="N33" s="6">
+      <c r="N33" s="48">
         <v>0</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="5">
         <v>0</v>
       </c>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-    </row>
-    <row r="34" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P33" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="44"/>
+    </row>
+    <row r="34" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>69</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6">
+        <v>67</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5">
         <v>3</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6" t="s">
+      <c r="D34" s="5"/>
+      <c r="E34" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <v>500</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <v>25</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <f>H34/I34</f>
         <v>20</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <v>6</v>
       </c>
-      <c r="L34" s="37">
+      <c r="L34" s="36">
         <f>IF(E34="Sjø",18,IF(E34="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M34" s="6">
-        <f>J34+K34+L34+O34</f>
+      <c r="M34" s="5">
+        <f>J34+K34+L34+P34</f>
         <v>50</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="48">
         <v>0</v>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="5">
         <v>0</v>
       </c>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-    </row>
-    <row r="35" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P34" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="44"/>
+    </row>
+    <row r="35" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6">
+        <v>67</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5">
         <v>4</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6" t="s">
+      <c r="D35" s="5"/>
+      <c r="E35" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="5">
         <v>600</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <v>25</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="5">
         <f>H35/I35</f>
         <v>24</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>4</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>IF(E35="Sjø",18,IF(E35="Truck",0,24))</f>
         <v>24</v>
       </c>
-      <c r="M35" s="6">
-        <f>J35+K35+L35+O35</f>
+      <c r="M35" s="5">
+        <f>J35+K35+L35+P35</f>
         <v>55</v>
       </c>
-      <c r="N35" s="6">
+      <c r="N35" s="48">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5">
         <v>1</v>
       </c>
-      <c r="O35" s="33">
+      <c r="P35" s="32">
         <v>3</v>
       </c>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-    </row>
-    <row r="36" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="8" t="s">
+      <c r="Q35" s="44"/>
+    </row>
+    <row r="36" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B36" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8">
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7">
         <f>SUM(H32:H35)</f>
         <v>2900</v>
       </c>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8">
-        <f t="shared" ref="J36:O36" si="3">SUM(J32:J35)</f>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7">
+        <f t="shared" ref="J36:M36" si="3">SUM(J32:J35)</f>
         <v>113</v>
       </c>
-      <c r="K36" s="8">
+      <c r="K36" s="7">
         <f t="shared" si="3"/>
         <v>28</v>
       </c>
-      <c r="L36" s="8">
+      <c r="L36" s="7">
         <f t="shared" si="3"/>
         <v>106</v>
       </c>
-      <c r="M36" s="8">
+      <c r="M36" s="7">
         <f t="shared" si="3"/>
         <v>250.5</v>
       </c>
-      <c r="N36" s="8">
-        <f t="shared" si="3"/>
+      <c r="N36" s="31">
+        <v>0</v>
+      </c>
+      <c r="O36" s="7">
+        <f>SUM(O32:O35)</f>
         <v>2</v>
       </c>
-      <c r="O36" s="34">
-        <f t="shared" si="3"/>
+      <c r="P36" s="33">
+        <f>SUM(P32:P35)</f>
         <v>3.5</v>
       </c>
-      <c r="P36" s="19">
+      <c r="Q36" s="47">
         <f>M36/24</f>
         <v>10.4375</v>
       </c>
-      <c r="Q36" s="19">
+    </row>
+    <row r="39" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="R36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B39" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="C39" s="33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="H39" s="33" t="s">
+      <c r="H39" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="I39" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="J39" s="33" t="s">
+      <c r="I39" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="J39" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="K39" s="33" t="s">
+      <c r="K39" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="L39" s="33" t="s">
+      <c r="L39" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="M39" s="33" t="s">
+      <c r="M39" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="N39" s="33" t="s">
+      <c r="N39" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="O39" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="O39" s="33" t="s">
+      <c r="P39" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="P39" s="33" t="s">
+      <c r="Q39" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="Q39" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="40" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>71</v>
-      </c>
-      <c r="B40" s="33"/>
-      <c r="C40" s="33">
+        <v>68</v>
+      </c>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32">
         <v>1</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E40" s="33" t="s">
+      <c r="E40" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="G40" s="33" t="s">
+      <c r="G40" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="33">
+      <c r="H40" s="32">
         <v>700</v>
       </c>
-      <c r="I40" s="33">
+      <c r="I40" s="32">
         <v>28</v>
       </c>
-      <c r="J40" s="33">
+      <c r="J40" s="32">
         <f>H40/I40</f>
         <v>25</v>
       </c>
-      <c r="K40" s="33">
+      <c r="K40" s="32">
         <v>12</v>
       </c>
-      <c r="L40" s="33">
+      <c r="L40" s="32">
         <f>IF(E40="Sjø",34,IF(E40="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M40" s="33">
-        <f>J40+K40+L40+O40</f>
+      <c r="M40" s="32">
+        <f>J40+K40+L40+P40</f>
         <v>71.5</v>
       </c>
-      <c r="N40" s="33">
+      <c r="N40" s="48">
+        <v>0</v>
+      </c>
+      <c r="O40" s="32">
         <v>1</v>
       </c>
-      <c r="O40" s="33">
+      <c r="P40" s="32">
         <v>0.5</v>
       </c>
-      <c r="P40" s="33"/>
-    </row>
-    <row r="41" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="Q40" s="32"/>
+    </row>
+    <row r="41" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>71</v>
-      </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33">
+        <v>68</v>
+      </c>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32">
         <v>2</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="G41" s="33" t="s">
+      <c r="G41" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="32">
         <v>3800</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="32">
         <v>33</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="32">
         <f>H41/I41</f>
         <v>115.15151515151516</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="32">
         <v>12</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="32">
         <f>IF(E41="Sjø",34,IF(E41="Truck",0,24))</f>
         <v>34</v>
       </c>
-      <c r="M41" s="33">
-        <f>J41+K41+L41+O41</f>
+      <c r="M41" s="32">
+        <f>J41+K41+L41+P41</f>
         <v>161.15151515151516</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="48">
         <v>0</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="32">
         <v>0</v>
       </c>
-      <c r="P41" s="33"/>
-    </row>
-    <row r="42" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="P41" s="32">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="32"/>
+    </row>
+    <row r="42" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>71</v>
-      </c>
-      <c r="B42" s="33"/>
-      <c r="C42" s="33">
+        <v>68</v>
+      </c>
+      <c r="B42" s="32"/>
+      <c r="C42" s="32">
         <v>3</v>
       </c>
-      <c r="D42" s="33" t="s">
+      <c r="D42" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="E42" s="33" t="s">
+      <c r="E42" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="G42" s="33" t="s">
+      <c r="G42" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="32">
         <v>476</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="32">
         <v>60</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="32">
         <f>H42/I42</f>
         <v>7.9333333333333336</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="32">
         <v>4</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="32">
         <f>IF(E42="Sjø",18,IF(E42="Truck",0,24))</f>
         <v>0</v>
       </c>
-      <c r="M42" s="33">
-        <f>J42+K42+L42+O42</f>
+      <c r="M42" s="32">
+        <f>J42+K42+L42+P42</f>
         <v>14.933333333333334</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="48">
+        <v>0</v>
+      </c>
+      <c r="O42" s="32">
         <v>1</v>
       </c>
-      <c r="O42" s="33">
+      <c r="P42" s="32">
         <v>3</v>
       </c>
-      <c r="P42" s="33"/>
-    </row>
-    <row r="43" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="34" t="s">
+      <c r="Q42" s="32"/>
+    </row>
+    <row r="43" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C43" s="34">
+      <c r="C43" s="33">
         <f>COUNT(C40:C42)</f>
         <v>3</v>
       </c>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34">
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33">
         <f>SUM(H40:H42)</f>
         <v>4976</v>
       </c>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34">
-        <f t="shared" ref="J43:O43" si="4">SUM(J40:J42)</f>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33">
+        <f t="shared" ref="J43:M43" si="4">SUM(J40:J42)</f>
         <v>148.08484848484849</v>
       </c>
-      <c r="K43" s="34">
+      <c r="K43" s="33">
         <f t="shared" si="4"/>
         <v>28</v>
       </c>
-      <c r="L43" s="34">
+      <c r="L43" s="33">
         <f t="shared" si="4"/>
         <v>68</v>
       </c>
-      <c r="M43" s="34">
+      <c r="M43" s="33">
         <f t="shared" si="4"/>
         <v>247.58484848484849</v>
       </c>
-      <c r="N43" s="34">
-        <f t="shared" si="4"/>
+      <c r="N43" s="31">
+        <v>0</v>
+      </c>
+      <c r="O43" s="33">
+        <f>SUM(O40:O42)</f>
         <v>2</v>
       </c>
-      <c r="O43" s="34">
-        <f t="shared" si="4"/>
+      <c r="P43" s="33">
+        <f>SUM(P40:P42)</f>
         <v>3.5</v>
       </c>
-      <c r="P43" s="42">
+      <c r="Q43" s="40">
         <f>M43/24</f>
         <v>10.316035353535353</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="B46" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="N46" s="48" t="s">
+        <v>168</v>
+      </c>
+      <c r="O46" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="P46" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>169</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H47" s="5">
+        <v>700</v>
+      </c>
+      <c r="I47" s="5">
+        <v>28</v>
+      </c>
+      <c r="J47" s="5">
+        <f>H47/I47</f>
+        <v>25</v>
+      </c>
+      <c r="K47" s="5">
+        <v>12</v>
+      </c>
+      <c r="L47" s="5">
+        <v>34</v>
+      </c>
+      <c r="M47" s="5">
+        <f>J47+K47+L47+N47+P47</f>
+        <v>71.5</v>
+      </c>
+      <c r="N47" s="48">
+        <v>0</v>
+      </c>
+      <c r="O47" s="5">
+        <v>1</v>
+      </c>
+      <c r="P47" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="Q47" s="5"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>169</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5">
+        <v>2</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="5">
+        <v>1780</v>
+      </c>
+      <c r="I48" s="5">
+        <v>60</v>
+      </c>
+      <c r="J48" s="5">
+        <f>H48/I48</f>
+        <v>29.666666666666668</v>
+      </c>
+      <c r="K48" s="5">
+        <v>4</v>
+      </c>
+      <c r="L48" s="5">
+        <v>18</v>
+      </c>
+      <c r="M48" s="5">
+        <f>J48+K48+L48+N48+P48</f>
+        <v>87.666666666666671</v>
+      </c>
+      <c r="N48" s="48">
+        <v>33</v>
+      </c>
+      <c r="O48" s="5">
+        <v>0</v>
+      </c>
+      <c r="P48" s="5">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="5"/>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B49" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C49" s="41">
+        <f>COUNT(C47:C48)</f>
+        <v>2</v>
+      </c>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41">
+        <f>SUM(H47:H48)</f>
+        <v>2480</v>
+      </c>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41">
+        <f t="shared" ref="J49:P49" si="5">SUM(J47:J48)</f>
+        <v>54.666666666666671</v>
+      </c>
+      <c r="K49" s="41">
+        <f t="shared" si="5"/>
+        <v>16</v>
+      </c>
+      <c r="L49" s="41">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="M49" s="41">
+        <f>SUM(M47:M48)</f>
+        <v>159.16666666666669</v>
+      </c>
+      <c r="N49" s="31">
+        <f>SUM(N47:N48)</f>
+        <v>33</v>
+      </c>
+      <c r="O49" s="41">
+        <v>1</v>
+      </c>
+      <c r="P49" s="41">
+        <f t="shared" si="5"/>
+        <v>3.5</v>
+      </c>
+      <c r="Q49" s="42">
+        <f>M49/24</f>
+        <v>6.6319444444444455</v>
       </c>
     </row>
   </sheetData>
@@ -4194,20 +4464,20 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="12">
         <v>330</v>
       </c>
       <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5">
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -4228,20 +4498,20 @@
       <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <v>0.5</v>
       </c>
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5">
         <v>2</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>20</v>
       </c>
       <c r="K3" s="3" t="s">
@@ -4260,22 +4530,22 @@
     </row>
     <row r="4" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6">
+        <v>166</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5">
         <v>3</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>23</v>
       </c>
       <c r="K4" s="3" t="s">
@@ -4296,21 +4566,21 @@
       <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <f>14/$B$9</f>
         <v>0.58333333333333337</v>
       </c>
       <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5">
         <v>4</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>28</v>
       </c>
       <c r="K5" s="3" t="s">
@@ -4334,14 +4604,14 @@
       <c r="B6">
         <v>1688</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5">
         <v>5</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>32</v>
       </c>
       <c r="K6" s="3" t="s">
@@ -4359,50 +4629,50 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>1200</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10">
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9">
         <f>SUM(M2:M6)</f>
         <v>31780</v>
       </c>
-      <c r="N7" s="10">
-        <f>$B$8*Ruter!N7</f>
+      <c r="N7" s="9">
+        <f>$B$8*Ruter!O7</f>
         <v>5064</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="9">
         <f>B2*Ruter!M7</f>
         <v>85132.142857142855</v>
       </c>
-      <c r="P7" s="15">
+      <c r="P7" s="14">
         <f>SUM(M7:O7)</f>
         <v>121976.14285714286</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>1688</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <v>24</v>
       </c>
       <c r="C9" t="s">
@@ -4442,20 +4712,20 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G11" s="6"/>
-      <c r="H11" s="6">
+      <c r="G11" s="5"/>
+      <c r="H11" s="5">
         <v>1</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="M11" s="3">
@@ -4467,20 +4737,20 @@
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G12" s="6"/>
-      <c r="H12" s="6">
+      <c r="G12" s="5"/>
+      <c r="H12" s="5">
         <v>2</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="5" t="s">
         <v>42</v>
       </c>
       <c r="M12" s="3">
@@ -4492,20 +4762,20 @@
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G13" s="6"/>
-      <c r="H13" s="6">
+      <c r="G13" s="5"/>
+      <c r="H13" s="5">
         <v>3</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M13" s="3">
@@ -4517,20 +4787,20 @@
       <c r="P13" s="3"/>
     </row>
     <row r="14" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G14" s="6"/>
-      <c r="H14" s="6">
+      <c r="G14" s="5"/>
+      <c r="H14" s="5">
         <v>4</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M14" s="3">
@@ -4542,37 +4812,37 @@
       <c r="P14" s="3"/>
     </row>
     <row r="15" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="10">
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="9">
         <f>SUM(M11:M14)</f>
         <v>27780</v>
       </c>
-      <c r="N15" s="10">
-        <f>$B$8*Ruter!N15</f>
+      <c r="N15" s="9">
+        <f>$B$8*Ruter!O15</f>
         <v>3376</v>
       </c>
-      <c r="O15" s="10">
+      <c r="O15" s="9">
         <f>$B$2*Ruter!M15</f>
         <v>79610.142857142855</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="16">
         <f>SUM(M15:O15)</f>
         <v>110766.14285714286</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P16" s="18"/>
+      <c r="P16" s="17"/>
     </row>
     <row r="17" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="18" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P18" s="18"/>
+      <c r="P18" s="17"/>
     </row>
     <row r="21" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G21" s="2" t="s">
@@ -4607,18 +4877,18 @@
       </c>
     </row>
     <row r="22" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G22" s="6"/>
-      <c r="H22" s="6">
+      <c r="G22" s="5"/>
+      <c r="H22" s="5">
         <v>1</v>
       </c>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6" t="s">
+      <c r="I22" s="5"/>
+      <c r="J22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="5" t="s">
         <v>45</v>
       </c>
       <c r="M22" s="3">
@@ -4630,18 +4900,18 @@
       <c r="P22" s="3"/>
     </row>
     <row r="23" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G23" s="6"/>
-      <c r="H23" s="6">
+      <c r="G23" s="5"/>
+      <c r="H23" s="5">
         <v>2</v>
       </c>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6" t="s">
+      <c r="I23" s="5"/>
+      <c r="J23" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K23" s="6" t="s">
+      <c r="K23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="5" t="s">
         <v>46</v>
       </c>
       <c r="M23" s="3">
@@ -4653,18 +4923,18 @@
       <c r="P23" s="3"/>
     </row>
     <row r="24" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G24" s="6"/>
-      <c r="H24" s="6">
+      <c r="G24" s="5"/>
+      <c r="H24" s="5">
         <v>3</v>
       </c>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6" t="s">
+      <c r="I24" s="5"/>
+      <c r="J24" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="M24" s="3">
@@ -4676,18 +4946,18 @@
       <c r="P24" s="3"/>
     </row>
     <row r="25" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G25" s="6"/>
-      <c r="H25" s="6">
+      <c r="G25" s="5"/>
+      <c r="H25" s="5">
         <v>4</v>
       </c>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6" t="s">
+      <c r="I25" s="5"/>
+      <c r="J25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M25" s="3">
@@ -4699,36 +4969,36 @@
       <c r="P25" s="3"/>
     </row>
     <row r="26" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="19"/>
-      <c r="M26" s="10">
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="9">
         <f>SUM(M22:M25)</f>
         <v>26500</v>
       </c>
-      <c r="N26" s="10">
-        <f>$B$8*Ruter!N26</f>
+      <c r="N26" s="9">
+        <f>$B$8*Ruter!O26</f>
         <v>3376</v>
       </c>
-      <c r="O26" s="10">
+      <c r="O26" s="9">
         <f>B2*Ruter!M26</f>
         <v>77385</v>
       </c>
-      <c r="P26" s="15">
+      <c r="P26" s="14">
         <f>SUM(M26:O26)</f>
         <v>107261</v>
       </c>
     </row>
     <row r="27" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P27" s="18"/>
+      <c r="P27" s="17"/>
     </row>
     <row r="30" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="5" t="s">
         <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
@@ -4760,18 +5030,18 @@
       </c>
     </row>
     <row r="31" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G31" s="6"/>
-      <c r="H31" s="6">
+      <c r="G31" s="5"/>
+      <c r="H31" s="5">
         <v>1</v>
       </c>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6" t="s">
+      <c r="I31" s="5"/>
+      <c r="J31" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="5" t="s">
         <v>45</v>
       </c>
       <c r="M31" s="3">
@@ -4783,18 +5053,18 @@
       <c r="P31" s="3"/>
     </row>
     <row r="32" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G32" s="6"/>
-      <c r="H32" s="6">
+      <c r="G32" s="5"/>
+      <c r="H32" s="5">
         <v>2</v>
       </c>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6" t="s">
+      <c r="I32" s="5"/>
+      <c r="J32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="5" t="s">
         <v>48</v>
       </c>
       <c r="M32" s="3">
@@ -4806,18 +5076,18 @@
       <c r="P32" s="3"/>
     </row>
     <row r="33" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G33" s="6"/>
-      <c r="H33" s="6">
+      <c r="G33" s="5"/>
+      <c r="H33" s="5">
         <v>3</v>
       </c>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6" t="s">
+      <c r="I33" s="5"/>
+      <c r="J33" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="K33" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="5" t="s">
         <v>49</v>
       </c>
       <c r="M33" s="3">
@@ -4829,18 +5099,18 @@
       <c r="P33" s="3"/>
     </row>
     <row r="34" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G34" s="6"/>
-      <c r="H34" s="6">
+      <c r="G34" s="5"/>
+      <c r="H34" s="5">
         <v>4</v>
       </c>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6" t="s">
+      <c r="I34" s="5"/>
+      <c r="J34" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="L34" s="5" t="s">
         <v>33</v>
       </c>
       <c r="M34" s="3">
@@ -4852,33 +5122,33 @@
       <c r="P34" s="3"/>
     </row>
     <row r="35" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G35" s="19" t="s">
+      <c r="G35" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="10">
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="9">
         <f>SUM(M31:M34)</f>
         <v>31300</v>
       </c>
-      <c r="N35" s="10">
-        <f>$B$8*Ruter!N36</f>
+      <c r="N35" s="9">
+        <f>$B$8*Ruter!O36</f>
         <v>3376</v>
       </c>
-      <c r="O35" s="10">
+      <c r="O35" s="9">
         <f>B2*Ruter!M36</f>
         <v>82665</v>
       </c>
-      <c r="P35" s="15">
+      <c r="P35" s="14">
         <f>SUM(M35:O35)</f>
         <v>117341</v>
       </c>
     </row>
     <row r="36" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="P36" s="18"/>
+      <c r="P36" s="17"/>
     </row>
     <row r="39" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="G39" s="3" t="s">
@@ -4988,27 +5258,27 @@
       <c r="P42" s="3"/>
     </row>
     <row r="43" spans="7:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10">
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9">
         <f>SUM(M40:M42)</f>
         <v>38164</v>
       </c>
-      <c r="N43" s="10">
-        <f>$B$8*Ruter!N43</f>
+      <c r="N43" s="9">
+        <f>$B$8*Ruter!O43</f>
         <v>3376</v>
       </c>
-      <c r="O43" s="10">
+      <c r="O43" s="9">
         <f>$B$2*Ruter!M43</f>
         <v>81703</v>
       </c>
-      <c r="P43" s="17">
+      <c r="P43" s="16">
         <f>SUM(M43:O43)</f>
         <v>123243</v>
       </c>
@@ -5031,7 +5301,7 @@
   <sheetData>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -5040,53 +5310,53 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="18">
+      <c r="A3" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="17">
         <f>Kostnadsmodeller!P7</f>
         <v>121976.14285714286</v>
       </c>
-      <c r="C3" s="11">
-        <f>Ruter!N7</f>
+      <c r="C3" s="10">
+        <f>Ruter!O7</f>
         <v>3</v>
       </c>
-      <c r="D3" s="21">
+      <c r="D3" s="20">
         <f>Ruter!M7</f>
         <v>257.97619047619048</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="18">
+      <c r="A4" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" s="17">
         <f>Kostnadsmodeller!P15</f>
         <v>110766.14285714286</v>
       </c>
-      <c r="C4" s="11">
-        <f>Ruter!N15</f>
+      <c r="C4" s="10">
+        <f>Ruter!O15</f>
         <v>2</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="20">
         <f>Ruter!M15</f>
         <v>241.24285714285713</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="18">
+      <c r="A5" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="17">
         <f>Kostnadsmodeller!P26</f>
         <v>107261</v>
       </c>
       <c r="C5">
-        <f>Ruter!N26</f>
+        <f>Ruter!O26</f>
         <v>2</v>
       </c>
       <c r="D5">
@@ -5095,15 +5365,15 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" s="18">
+      <c r="A6" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="17">
         <f>Kostnadsmodeller!P35</f>
         <v>117341</v>
       </c>
       <c r="C6">
-        <f>Ruter!N36</f>
+        <f>Ruter!O36</f>
         <v>2</v>
       </c>
       <c r="D6">
@@ -5113,14 +5383,14 @@
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="18">
+        <v>68</v>
+      </c>
+      <c r="B7" s="17">
         <f>Kostnadsmodeller!P43</f>
         <v>123243</v>
       </c>
       <c r="C7">
-        <f>Ruter!N43</f>
+        <f>Ruter!O43</f>
         <v>2</v>
       </c>
       <c r="D7">
@@ -5149,556 +5419,556 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="47" t="s">
+      <c r="C5" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="49" t="s">
+      <c r="D5" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="E5" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="25" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="C6" s="26">
+        <v>0.12</v>
+      </c>
+      <c r="D6" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E6" s="25" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="26" t="s">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="27">
-        <v>0.12</v>
-      </c>
-      <c r="D6" s="26" t="s">
+      <c r="B7" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="26">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E7" s="25" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="26" t="s">
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="26">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B7" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="27">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="E8" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="26" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="26">
+        <v>0.08</v>
+      </c>
+      <c r="D9" s="25" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="27">
-        <v>0.2</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="E9" s="25" t="s">
         <v>87</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="27">
-        <v>0.08</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="25" t="s">
+      <c r="D13" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="E13" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="27">
+        <v>6</v>
+      </c>
+      <c r="C14" s="27">
+        <v>12</v>
+      </c>
+      <c r="D14" s="27">
+        <v>24</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="F14" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="25" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="29">
+        <v>8</v>
+      </c>
+      <c r="C15" s="29">
+        <v>12</v>
+      </c>
+      <c r="D15" s="29">
+        <v>24</v>
+      </c>
+      <c r="E15" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="28">
+      <c r="F15" s="28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="27">
+        <v>3</v>
+      </c>
+      <c r="C16" s="27">
         <v>6</v>
       </c>
-      <c r="C14" s="28">
+      <c r="D16" s="27">
         <v>12</v>
       </c>
-      <c r="D14" s="28">
-        <v>24</v>
-      </c>
-      <c r="E14" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="F14" s="26" t="s">
+      <c r="E16" s="25" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" s="30">
+      <c r="F16" s="25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="27">
+        <v>2</v>
+      </c>
+      <c r="C17" s="27">
+        <v>4</v>
+      </c>
+      <c r="D17" s="27">
         <v>8</v>
       </c>
-      <c r="C15" s="30">
-        <v>12</v>
-      </c>
-      <c r="D15" s="30">
-        <v>24</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="F15" s="29" t="s">
+      <c r="E17" s="25" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="28">
-        <v>3</v>
-      </c>
-      <c r="C16" s="28">
-        <v>6</v>
-      </c>
-      <c r="D16" s="28">
-        <v>12</v>
-      </c>
-      <c r="E16" s="26" t="s">
+      <c r="F17" s="25" t="s">
         <v>100</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="28">
-        <v>2</v>
-      </c>
-      <c r="C17" s="28">
-        <v>4</v>
-      </c>
-      <c r="D17" s="28">
-        <v>8</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="24" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="23" t="s">
+      <c r="D22" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="27">
+        <v>68</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="25" t="s">
+      <c r="D23" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="25" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="27">
+        <v>68</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="D22" s="25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="28">
-        <v>68</v>
-      </c>
-      <c r="C23" s="26" t="s">
+      <c r="D24" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="26" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="27">
+        <v>48</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B24" s="28">
-        <v>68</v>
-      </c>
-      <c r="C24" s="26" t="s">
+      <c r="D25" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="D24" s="26" t="s">
+    </row>
+    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="29">
+        <v>0</v>
+      </c>
+      <c r="C26" s="28" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="28">
-        <v>48</v>
-      </c>
-      <c r="C25" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="30">
-        <v>0</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>103</v>
+      <c r="D26" s="28" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="43"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
+      <c r="A27" s="50"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="27">
+        <v>0.25</v>
+      </c>
+      <c r="C31" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="D31" s="27">
+        <v>1</v>
+      </c>
+      <c r="E31" s="25" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="25" t="s">
+      <c r="F31" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="B30" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="25" t="s">
+    </row>
+    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="27">
+        <v>2</v>
+      </c>
+      <c r="C32" s="27">
+        <v>3</v>
+      </c>
+      <c r="D32" s="27">
         <v>5</v>
       </c>
-      <c r="D30" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="F30" s="25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" s="28">
-        <v>0.25</v>
-      </c>
-      <c r="C31" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="D31" s="28">
-        <v>1</v>
-      </c>
-      <c r="E31" s="26" t="s">
+      <c r="E32" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="F31" s="26" t="s">
+      <c r="F32" s="25" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="26" t="s">
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="28">
-        <v>2</v>
-      </c>
-      <c r="C32" s="28">
-        <v>3</v>
-      </c>
-      <c r="D32" s="28">
-        <v>5</v>
-      </c>
-      <c r="E32" s="26" t="s">
+      <c r="B33" s="27">
+        <v>0</v>
+      </c>
+      <c r="C33" s="27">
+        <v>0</v>
+      </c>
+      <c r="D33" s="27">
+        <v>0</v>
+      </c>
+      <c r="E33" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="F32" s="26" t="s">
+      <c r="F33" s="25" t="s">
         <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="B33" s="28">
-        <v>0</v>
-      </c>
-      <c r="C33" s="28">
-        <v>0</v>
-      </c>
-      <c r="D33" s="28">
-        <v>0</v>
-      </c>
-      <c r="E33" s="26" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" s="26" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="36" spans="1:6" ht="15.4" x14ac:dyDescent="0.45">
-      <c r="A36" s="24" t="s">
+      <c r="A36" s="23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A37" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="53"/>
+    </row>
+    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="C39" s="27">
+        <v>12</v>
+      </c>
+      <c r="D39" s="27">
+        <v>24</v>
+      </c>
+      <c r="E39" s="27">
+        <v>72</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="27">
+        <v>0.05</v>
+      </c>
+      <c r="C40" s="27">
+        <v>12</v>
+      </c>
+      <c r="D40" s="27">
+        <v>24</v>
+      </c>
+      <c r="E40" s="27">
+        <v>72</v>
+      </c>
+      <c r="F40" s="25" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A37" s="23" t="s">
+    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="27">
+        <v>0.08</v>
+      </c>
+      <c r="C41" s="27">
+        <v>12</v>
+      </c>
+      <c r="D41" s="27">
+        <v>24</v>
+      </c>
+      <c r="E41" s="27">
+        <v>72</v>
+      </c>
+      <c r="F41" s="25" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="45"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="45"/>
-      <c r="F38" s="46"/>
-    </row>
-    <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" s="28">
-        <v>0.05</v>
-      </c>
-      <c r="C39" s="28">
+    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="27">
+        <v>0.03</v>
+      </c>
+      <c r="C42" s="27">
+        <v>4</v>
+      </c>
+      <c r="D42" s="27">
         <v>12</v>
       </c>
-      <c r="D39" s="28">
+      <c r="E42" s="27">
         <v>24</v>
       </c>
-      <c r="E39" s="28">
-        <v>72</v>
-      </c>
-      <c r="F39" s="26" t="s">
+      <c r="F42" s="25" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="B40" s="28">
-        <v>0.05</v>
-      </c>
-      <c r="C40" s="28">
-        <v>12</v>
-      </c>
-      <c r="D40" s="28">
-        <v>24</v>
-      </c>
-      <c r="E40" s="28">
-        <v>72</v>
-      </c>
-      <c r="F40" s="26" t="s">
+    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="56" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A41" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="28">
-        <v>0.08</v>
-      </c>
-      <c r="C41" s="28">
-        <v>12</v>
-      </c>
-      <c r="D41" s="28">
-        <v>24</v>
-      </c>
-      <c r="E41" s="28">
-        <v>72</v>
-      </c>
-      <c r="F41" s="26" t="s">
+      <c r="B45" s="50"/>
+      <c r="C45" s="50"/>
+      <c r="D45" s="50"/>
+      <c r="E45" s="50"/>
+      <c r="F45" s="50"/>
+    </row>
+    <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="51" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" s="28">
-        <v>0.03</v>
-      </c>
-      <c r="C42" s="28">
-        <v>4</v>
-      </c>
-      <c r="D42" s="28">
-        <v>12</v>
-      </c>
-      <c r="E42" s="28">
-        <v>24</v>
-      </c>
-      <c r="F42" s="26" t="s">
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="53"/>
+    </row>
+    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="25" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="49" t="s">
+      <c r="B47" s="27">
+        <v>10000</v>
+      </c>
+      <c r="C47" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-    </row>
-    <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="44" t="s">
+    </row>
+    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="45"/>
-      <c r="E46" s="45"/>
-      <c r="F46" s="46"/>
-    </row>
-    <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A47" s="26" t="s">
+      <c r="B48" s="27">
+        <v>42</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="28">
-        <v>10000</v>
-      </c>
-      <c r="C47" s="26" t="s">
+    </row>
+    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="25" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A48" s="26" t="s">
+      <c r="B49" s="27">
+        <v>0</v>
+      </c>
+      <c r="C49" s="25" t="s">
         <v>136</v>
-      </c>
-      <c r="B48" s="28">
-        <v>42</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A49" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="B49" s="28">
-        <v>0</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5707,12 +5977,12 @@
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="43"/>
-      <c r="B57" s="43"/>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
+      <c r="A57" s="50"/>
+      <c r="B57" s="50"/>
+      <c r="C57" s="50"/>
+      <c r="D57" s="50"/>
+      <c r="E57" s="50"/>
+      <c r="F57" s="50"/>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5746,170 +6016,170 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+    </row>
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="54" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="47" t="s">
+      <c r="D4" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" s="25" t="s">
+      <c r="B5" s="27">
+        <v>330</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="D5" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="26" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="28">
-        <v>330</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="B6" s="27">
+        <v>0.8</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D6" s="25" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="26" t="s">
+    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="28">
-        <v>0.8</v>
-      </c>
-      <c r="C6" s="26" t="s">
+      <c r="B7" s="27">
+        <v>0.5</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D7" s="25" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="26" t="s">
+    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="28">
-        <v>0.5</v>
-      </c>
-      <c r="C7" s="26" t="s">
+      <c r="B8" s="27">
+        <v>0.58330000000000004</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="26" t="s">
+    </row>
+    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="25" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="26" t="s">
+      <c r="B9" s="30">
+        <v>7</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="28">
-        <v>0.58330000000000004</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="D9" s="25" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="26" t="s">
+    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="31">
-        <v>7</v>
-      </c>
-      <c r="C9" s="26" t="s">
+      <c r="B10" s="27">
+        <v>0</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D10" s="25" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="26" t="s">
+    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="B10" s="28">
-        <v>0</v>
-      </c>
-      <c r="C10" s="26" t="s">
+      <c r="B11" s="27">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="B12" s="27">
+        <v>24</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="26" t="s">
+      <c r="D12" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="B11" s="28">
-        <v>1000</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>159</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="26" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="B12" s="28">
-        <v>24</v>
-      </c>
-      <c r="C12" s="26" t="s">
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+    </row>
+    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+    </row>
+    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="54" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="47" t="s">
-        <v>166</v>
-      </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="47" t="s">
-        <v>167</v>
-      </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="5">
